--- a/report/models/dev_v1_expand_model_comparison.xlsx
+++ b/report/models/dev_v1_expand_model_comparison.xlsx
@@ -179,7 +179,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -193,6 +193,7 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -573,8 +574,8 @@
   <dimension ref="A1:V11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
@@ -600,12 +601,12 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
+          <t>mode</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
           <t>language</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>mode</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
@@ -756,12 +757,12 @@
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
+          <t>no_term</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
           <t>ende</t>
-        </is>
-      </c>
-      <c r="B3" s="5" t="inlineStr">
-        <is>
-          <t>no_term</t>
         </is>
       </c>
       <c r="C3" s="5" t="n">
@@ -824,24 +825,20 @@
       <c r="V3" s="5" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="5" t="inlineStr">
-        <is>
-          <t>ende</t>
-        </is>
-      </c>
+      <c r="A4" s="7" t="n"/>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>proper_term</t>
+          <t>enru</t>
         </is>
       </c>
       <c r="C4" s="5" t="n">
-        <v>53.1453355808675</v>
+        <v>28.88618515581948</v>
       </c>
       <c r="D4" s="5" t="n">
-        <v>35.35130261696263</v>
+        <v>22.2122743557618</v>
       </c>
       <c r="E4" s="5" t="n">
-        <v>40.7526662444401</v>
+        <v>23.94330515356511</v>
       </c>
       <c r="F4" s="6" t="inlineStr">
         <is>
@@ -849,13 +846,13 @@
         </is>
       </c>
       <c r="G4" s="5" t="n">
-        <v>77.62256268271634</v>
+        <v>59.40396775797693</v>
       </c>
       <c r="H4" s="5" t="n">
-        <v>67.49950716527168</v>
+        <v>51.15009393251925</v>
       </c>
       <c r="I4" s="5" t="n">
-        <v>70.86410519427808</v>
+        <v>52.55814272287282</v>
       </c>
       <c r="J4" s="6" t="inlineStr">
         <is>
@@ -863,149 +860,121 @@
         </is>
       </c>
       <c r="K4" s="5" t="n">
-        <v>74.98295841854123</v>
+        <v/>
       </c>
       <c r="L4" s="5" t="n">
-        <v>67.41649625085208</v>
+        <v/>
       </c>
       <c r="M4" s="5" t="n">
-        <v>70.3817314246762</v>
-      </c>
-      <c r="N4" s="6" t="inlineStr">
-        <is>
-          <t>GPT</t>
-        </is>
-      </c>
+        <v/>
+      </c>
+      <c r="N4" s="5" t="n"/>
       <c r="O4" s="5" t="n">
-        <v>0.9444055155334643</v>
+        <v/>
       </c>
       <c r="P4" s="5" t="n">
-        <v>0.9328954887283994</v>
+        <v/>
       </c>
       <c r="Q4" s="5" t="n">
-        <v>0.9402285151418706</v>
-      </c>
-      <c r="R4" s="6" t="inlineStr">
-        <is>
-          <t>GPT</t>
-        </is>
-      </c>
+        <v/>
+      </c>
+      <c r="R4" s="5" t="n"/>
       <c r="S4" s="5" t="n">
-        <v>0.8634772462077019</v>
+        <v/>
       </c>
       <c r="T4" s="5" t="n">
-        <v>0.8366394399066506</v>
+        <v/>
       </c>
       <c r="U4" s="5" t="n">
-        <v>0.8553092182030346</v>
-      </c>
-      <c r="V4" s="6" t="inlineStr">
-        <is>
-          <t>GPT</t>
-        </is>
-      </c>
+        <v/>
+      </c>
+      <c r="V4" s="5" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="7" t="inlineStr">
-        <is>
-          <t>ende</t>
-        </is>
-      </c>
-      <c r="B5" s="7" t="inlineStr">
-        <is>
-          <t>random_term</t>
-        </is>
-      </c>
-      <c r="C5" s="7" t="n">
-        <v>45.4184376722181</v>
-      </c>
-      <c r="D5" s="7" t="n">
-        <v>28.05223765727727</v>
-      </c>
-      <c r="E5" s="7" t="n">
-        <v>33.80988013594433</v>
-      </c>
-      <c r="F5" s="8" t="inlineStr">
-        <is>
-          <t>GPT</t>
-        </is>
-      </c>
-      <c r="G5" s="7" t="n">
-        <v>70.67961683738467</v>
-      </c>
-      <c r="H5" s="7" t="n">
-        <v>58.99719589489819</v>
-      </c>
-      <c r="I5" s="7" t="n">
-        <v>62.73102319361662</v>
-      </c>
-      <c r="J5" s="8" t="inlineStr">
-        <is>
-          <t>GPT</t>
-        </is>
-      </c>
-      <c r="K5" s="7" t="n">
-        <v>82.76385725132879</v>
-      </c>
-      <c r="L5" s="7" t="n">
-        <v>69.43811693242218</v>
-      </c>
-      <c r="M5" s="7" t="n">
-        <v>76.80334092634776</v>
-      </c>
-      <c r="N5" s="8" t="inlineStr">
-        <is>
-          <t>GPT</t>
-        </is>
-      </c>
-      <c r="O5" s="7" t="n">
-        <v>0.948272961424509</v>
-      </c>
-      <c r="P5" s="7" t="n">
-        <v>0.9436337784924144</v>
-      </c>
-      <c r="Q5" s="7" t="n">
-        <v>0.9465645331784954</v>
-      </c>
-      <c r="R5" s="8" t="inlineStr">
-        <is>
-          <t>GPT</t>
-        </is>
-      </c>
-      <c r="S5" s="7" t="n">
-        <v>0.8835725677830941</v>
-      </c>
-      <c r="T5" s="7" t="n">
-        <v>0.8724082934609246</v>
-      </c>
-      <c r="U5" s="7" t="n">
-        <v>0.8803827751196173</v>
-      </c>
-      <c r="V5" s="8" t="inlineStr">
-        <is>
-          <t>GPT</t>
-        </is>
-      </c>
+      <c r="A5" s="4" t="n"/>
+      <c r="B5" s="8" t="inlineStr">
+        <is>
+          <t>enes</t>
+        </is>
+      </c>
+      <c r="C5" s="8" t="n">
+        <v>48.47964848343948</v>
+      </c>
+      <c r="D5" s="8" t="n">
+        <v>37.70802575962966</v>
+      </c>
+      <c r="E5" s="8" t="n">
+        <v>41.78029803732601</v>
+      </c>
+      <c r="F5" s="9" t="inlineStr">
+        <is>
+          <t>GPT</t>
+        </is>
+      </c>
+      <c r="G5" s="8" t="n">
+        <v>69.480952710827</v>
+      </c>
+      <c r="H5" s="8" t="n">
+        <v>63.26328009575467</v>
+      </c>
+      <c r="I5" s="8" t="n">
+        <v>65.72906973208383</v>
+      </c>
+      <c r="J5" s="9" t="inlineStr">
+        <is>
+          <t>GPT</t>
+        </is>
+      </c>
+      <c r="K5" s="8" t="n">
+        <v/>
+      </c>
+      <c r="L5" s="8" t="n">
+        <v/>
+      </c>
+      <c r="M5" s="8" t="n">
+        <v/>
+      </c>
+      <c r="N5" s="8" t="n"/>
+      <c r="O5" s="8" t="n">
+        <v/>
+      </c>
+      <c r="P5" s="8" t="n">
+        <v/>
+      </c>
+      <c r="Q5" s="8" t="n">
+        <v/>
+      </c>
+      <c r="R5" s="8" t="n"/>
+      <c r="S5" s="8" t="n">
+        <v/>
+      </c>
+      <c r="T5" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U5" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V5" s="8" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>enru</t>
+          <t>proper_term</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>no_term</t>
+          <t>ende</t>
         </is>
       </c>
       <c r="C6" s="5" t="n">
-        <v>28.88618515581948</v>
+        <v>53.1453355808675</v>
       </c>
       <c r="D6" s="5" t="n">
-        <v>22.2122743557618</v>
+        <v>35.35130261696263</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>23.94330515356511</v>
+        <v>40.7526662444401</v>
       </c>
       <c r="F6" s="6" t="inlineStr">
         <is>
@@ -1013,13 +982,13 @@
         </is>
       </c>
       <c r="G6" s="5" t="n">
-        <v>59.40396775797693</v>
+        <v>77.62256268271634</v>
       </c>
       <c r="H6" s="5" t="n">
-        <v>51.15009393251925</v>
+        <v>67.49950716527168</v>
       </c>
       <c r="I6" s="5" t="n">
-        <v>52.55814272287282</v>
+        <v>70.86410519427808</v>
       </c>
       <c r="J6" s="6" t="inlineStr">
         <is>
@@ -1027,45 +996,53 @@
         </is>
       </c>
       <c r="K6" s="5" t="n">
-        <v/>
+        <v>74.98295841854123</v>
       </c>
       <c r="L6" s="5" t="n">
-        <v/>
+        <v>67.41649625085208</v>
       </c>
       <c r="M6" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N6" s="5" t="n"/>
+        <v>70.3817314246762</v>
+      </c>
+      <c r="N6" s="6" t="inlineStr">
+        <is>
+          <t>GPT</t>
+        </is>
+      </c>
       <c r="O6" s="5" t="n">
-        <v/>
+        <v>0.9444055155334643</v>
       </c>
       <c r="P6" s="5" t="n">
-        <v/>
+        <v>0.9328954887283994</v>
       </c>
       <c r="Q6" s="5" t="n">
-        <v/>
-      </c>
-      <c r="R6" s="5" t="n"/>
+        <v>0.9402285151418706</v>
+      </c>
+      <c r="R6" s="6" t="inlineStr">
+        <is>
+          <t>GPT</t>
+        </is>
+      </c>
       <c r="S6" s="5" t="n">
-        <v/>
+        <v>0.8634772462077019</v>
       </c>
       <c r="T6" s="5" t="n">
-        <v/>
+        <v>0.8366394399066506</v>
       </c>
       <c r="U6" s="5" t="n">
-        <v/>
-      </c>
-      <c r="V6" s="5" t="n"/>
+        <v>0.8553092182030346</v>
+      </c>
+      <c r="V6" s="6" t="inlineStr">
+        <is>
+          <t>GPT</t>
+        </is>
+      </c>
     </row>
     <row r="7">
-      <c r="A7" s="5" t="inlineStr">
+      <c r="A7" s="7" t="n"/>
+      <c r="B7" s="5" t="inlineStr">
         <is>
           <t>enru</t>
-        </is>
-      </c>
-      <c r="B7" s="5" t="inlineStr">
-        <is>
-          <t>proper_term</t>
         </is>
       </c>
       <c r="C7" s="5" t="n">
@@ -1140,82 +1117,78 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="7" t="inlineStr">
-        <is>
-          <t>enru</t>
-        </is>
-      </c>
-      <c r="B8" s="7" t="inlineStr">
-        <is>
-          <t>random_term</t>
-        </is>
-      </c>
-      <c r="C8" s="7" t="n">
-        <v>31.83376452763599</v>
-      </c>
-      <c r="D8" s="7" t="n">
-        <v>22.03946931045422</v>
-      </c>
-      <c r="E8" s="7" t="n">
-        <v>27.51452427307115</v>
-      </c>
-      <c r="F8" s="8" t="inlineStr">
-        <is>
-          <t>GPT</t>
-        </is>
-      </c>
-      <c r="G8" s="7" t="n">
-        <v>62.90799354344954</v>
-      </c>
-      <c r="H8" s="7" t="n">
-        <v>51.06597598024478</v>
-      </c>
-      <c r="I8" s="7" t="n">
-        <v>56.8364355515637</v>
-      </c>
-      <c r="J8" s="8" t="inlineStr">
-        <is>
-          <t>GPT</t>
-        </is>
-      </c>
-      <c r="K8" s="7" t="n">
-        <v>81.51478816946441</v>
-      </c>
-      <c r="L8" s="7" t="n">
-        <v>65.18784972022381</v>
-      </c>
-      <c r="M8" s="7" t="n">
-        <v>74.92006394884092</v>
-      </c>
-      <c r="N8" s="8" t="inlineStr">
-        <is>
-          <t>GPT</t>
-        </is>
-      </c>
-      <c r="O8" s="7" t="n">
-        <v>0.9302609860163819</v>
-      </c>
-      <c r="P8" s="7" t="n">
-        <v>0.9262823507427826</v>
-      </c>
-      <c r="Q8" s="7" t="n">
-        <v>0.9254648229468374</v>
-      </c>
-      <c r="R8" s="8" t="inlineStr">
-        <is>
-          <t>GPT</t>
-        </is>
-      </c>
-      <c r="S8" s="7" t="n">
-        <v>0.855871886120997</v>
-      </c>
-      <c r="T8" s="7" t="n">
-        <v>0.8469750889679717</v>
-      </c>
-      <c r="U8" s="7" t="n">
-        <v>0.8416370106761575</v>
-      </c>
-      <c r="V8" s="8" t="inlineStr">
+      <c r="A8" s="4" t="n"/>
+      <c r="B8" s="8" t="inlineStr">
+        <is>
+          <t>enes</t>
+        </is>
+      </c>
+      <c r="C8" s="8" t="n">
+        <v>65.50039397469644</v>
+      </c>
+      <c r="D8" s="8" t="n">
+        <v>53.02564888932073</v>
+      </c>
+      <c r="E8" s="8" t="n">
+        <v>60.71345945287555</v>
+      </c>
+      <c r="F8" s="9" t="inlineStr">
+        <is>
+          <t>GPT</t>
+        </is>
+      </c>
+      <c r="G8" s="8" t="n">
+        <v>82.2376779517852</v>
+      </c>
+      <c r="H8" s="8" t="n">
+        <v>74.20603887944995</v>
+      </c>
+      <c r="I8" s="8" t="n">
+        <v>79.39122185435912</v>
+      </c>
+      <c r="J8" s="9" t="inlineStr">
+        <is>
+          <t>GPT</t>
+        </is>
+      </c>
+      <c r="K8" s="8" t="n">
+        <v>93.16479400749064</v>
+      </c>
+      <c r="L8" s="8" t="n">
+        <v>84.6441947565543</v>
+      </c>
+      <c r="M8" s="8" t="n">
+        <v>91.19850187265918</v>
+      </c>
+      <c r="N8" s="9" t="inlineStr">
+        <is>
+          <t>GPT</t>
+        </is>
+      </c>
+      <c r="O8" s="8" t="n">
+        <v>0.9592626054286718</v>
+      </c>
+      <c r="P8" s="8" t="n">
+        <v>0.952411616990798</v>
+      </c>
+      <c r="Q8" s="8" t="n">
+        <v>0.9571928135673363</v>
+      </c>
+      <c r="R8" s="9" t="inlineStr">
+        <is>
+          <t>GPT</t>
+        </is>
+      </c>
+      <c r="S8" s="8" t="n">
+        <v>0.8735262593783482</v>
+      </c>
+      <c r="T8" s="8" t="n">
+        <v>0.8510182207931405</v>
+      </c>
+      <c r="U8" s="8" t="n">
+        <v>0.8703108252947471</v>
+      </c>
+      <c r="V8" s="9" t="inlineStr">
         <is>
           <t>GPT</t>
         </is>
@@ -1224,22 +1197,22 @@
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>enes</t>
+          <t>random_term</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>no_term</t>
+          <t>ende</t>
         </is>
       </c>
       <c r="C9" s="5" t="n">
-        <v>48.47964848343948</v>
+        <v>45.4184376722181</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>37.70802575962966</v>
+        <v>28.05223765727727</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>41.78029803732601</v>
+        <v>33.80988013594433</v>
       </c>
       <c r="F9" s="6" t="inlineStr">
         <is>
@@ -1247,13 +1220,13 @@
         </is>
       </c>
       <c r="G9" s="5" t="n">
-        <v>69.480952710827</v>
+        <v>70.67961683738467</v>
       </c>
       <c r="H9" s="5" t="n">
-        <v>63.26328009575467</v>
+        <v>58.99719589489819</v>
       </c>
       <c r="I9" s="5" t="n">
-        <v>65.72906973208383</v>
+        <v>62.73102319361662</v>
       </c>
       <c r="J9" s="6" t="inlineStr">
         <is>
@@ -1261,55 +1234,63 @@
         </is>
       </c>
       <c r="K9" s="5" t="n">
-        <v/>
+        <v>82.76385725132879</v>
       </c>
       <c r="L9" s="5" t="n">
-        <v/>
+        <v>69.43811693242218</v>
       </c>
       <c r="M9" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N9" s="5" t="n"/>
+        <v>76.80334092634776</v>
+      </c>
+      <c r="N9" s="6" t="inlineStr">
+        <is>
+          <t>GPT</t>
+        </is>
+      </c>
       <c r="O9" s="5" t="n">
-        <v/>
+        <v>0.948272961424509</v>
       </c>
       <c r="P9" s="5" t="n">
-        <v/>
+        <v>0.9436337784924144</v>
       </c>
       <c r="Q9" s="5" t="n">
-        <v/>
-      </c>
-      <c r="R9" s="5" t="n"/>
+        <v>0.9465645331784954</v>
+      </c>
+      <c r="R9" s="6" t="inlineStr">
+        <is>
+          <t>GPT</t>
+        </is>
+      </c>
       <c r="S9" s="5" t="n">
-        <v/>
+        <v>0.8835725677830941</v>
       </c>
       <c r="T9" s="5" t="n">
-        <v/>
+        <v>0.8724082934609246</v>
       </c>
       <c r="U9" s="5" t="n">
-        <v/>
-      </c>
-      <c r="V9" s="5" t="n"/>
+        <v>0.8803827751196173</v>
+      </c>
+      <c r="V9" s="6" t="inlineStr">
+        <is>
+          <t>GPT</t>
+        </is>
+      </c>
     </row>
     <row r="10">
-      <c r="A10" s="5" t="inlineStr">
-        <is>
-          <t>enes</t>
-        </is>
-      </c>
+      <c r="A10" s="7" t="n"/>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>proper_term</t>
+          <t>enru</t>
         </is>
       </c>
       <c r="C10" s="5" t="n">
-        <v>65.50039397469644</v>
+        <v>31.83376452763599</v>
       </c>
       <c r="D10" s="5" t="n">
-        <v>53.02564888932073</v>
+        <v>22.03946931045422</v>
       </c>
       <c r="E10" s="5" t="n">
-        <v>60.71345945287555</v>
+        <v>27.51452427307115</v>
       </c>
       <c r="F10" s="6" t="inlineStr">
         <is>
@@ -1317,13 +1298,13 @@
         </is>
       </c>
       <c r="G10" s="5" t="n">
-        <v>82.2376779517852</v>
+        <v>62.90799354344954</v>
       </c>
       <c r="H10" s="5" t="n">
-        <v>74.20603887944995</v>
+        <v>51.06597598024478</v>
       </c>
       <c r="I10" s="5" t="n">
-        <v>79.39122185435912</v>
+        <v>56.8364355515637</v>
       </c>
       <c r="J10" s="6" t="inlineStr">
         <is>
@@ -1331,13 +1312,13 @@
         </is>
       </c>
       <c r="K10" s="5" t="n">
-        <v>93.16479400749064</v>
+        <v>81.51478816946441</v>
       </c>
       <c r="L10" s="5" t="n">
-        <v>84.6441947565543</v>
+        <v>65.18784972022381</v>
       </c>
       <c r="M10" s="5" t="n">
-        <v>91.19850187265918</v>
+        <v>74.92006394884092</v>
       </c>
       <c r="N10" s="6" t="inlineStr">
         <is>
@@ -1345,13 +1326,13 @@
         </is>
       </c>
       <c r="O10" s="5" t="n">
-        <v>0.9592626054286718</v>
+        <v>0.9302609860163819</v>
       </c>
       <c r="P10" s="5" t="n">
-        <v>0.952411616990798</v>
+        <v>0.9262823507427826</v>
       </c>
       <c r="Q10" s="5" t="n">
-        <v>0.9571928135673363</v>
+        <v>0.9254648229468374</v>
       </c>
       <c r="R10" s="6" t="inlineStr">
         <is>
@@ -1359,13 +1340,13 @@
         </is>
       </c>
       <c r="S10" s="5" t="n">
-        <v>0.8735262593783482</v>
+        <v>0.855871886120997</v>
       </c>
       <c r="T10" s="5" t="n">
-        <v>0.8510182207931405</v>
+        <v>0.8469750889679717</v>
       </c>
       <c r="U10" s="5" t="n">
-        <v>0.8703108252947471</v>
+        <v>0.8416370106761575</v>
       </c>
       <c r="V10" s="6" t="inlineStr">
         <is>
@@ -1374,94 +1355,93 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="7" t="inlineStr">
+      <c r="A11" s="4" t="n"/>
+      <c r="B11" s="8" t="inlineStr">
         <is>
           <t>enes</t>
         </is>
       </c>
-      <c r="B11" s="7" t="inlineStr">
-        <is>
-          <t>random_term</t>
-        </is>
-      </c>
-      <c r="C11" s="7" t="n">
+      <c r="C11" s="8" t="n">
         <v>50.91611599987797</v>
       </c>
-      <c r="D11" s="7" t="n">
+      <c r="D11" s="8" t="n">
         <v>40.30633369781593</v>
       </c>
-      <c r="E11" s="7" t="n">
+      <c r="E11" s="8" t="n">
         <v>44.74056269758604</v>
       </c>
-      <c r="F11" s="8" t="inlineStr">
-        <is>
-          <t>GPT</t>
-        </is>
-      </c>
-      <c r="G11" s="7" t="n">
+      <c r="F11" s="9" t="inlineStr">
+        <is>
+          <t>GPT</t>
+        </is>
+      </c>
+      <c r="G11" s="8" t="n">
         <v>72.86417493654305</v>
       </c>
-      <c r="H11" s="7" t="n">
+      <c r="H11" s="8" t="n">
         <v>65.61876238085196</v>
       </c>
-      <c r="I11" s="7" t="n">
+      <c r="I11" s="8" t="n">
         <v>68.50737573789145</v>
       </c>
-      <c r="J11" s="8" t="inlineStr">
-        <is>
-          <t>GPT</t>
-        </is>
-      </c>
-      <c r="K11" s="7" t="n">
+      <c r="J11" s="9" t="inlineStr">
+        <is>
+          <t>GPT</t>
+        </is>
+      </c>
+      <c r="K11" s="8" t="n">
         <v>96.07594936708861</v>
       </c>
-      <c r="L11" s="7" t="n">
+      <c r="L11" s="8" t="n">
         <v>88.48101265822785</v>
       </c>
-      <c r="M11" s="7" t="n">
+      <c r="M11" s="8" t="n">
         <v>93.79746835443038</v>
       </c>
-      <c r="N11" s="8" t="inlineStr">
-        <is>
-          <t>GPT</t>
-        </is>
-      </c>
-      <c r="O11" s="7" t="n">
+      <c r="N11" s="9" t="inlineStr">
+        <is>
+          <t>GPT</t>
+        </is>
+      </c>
+      <c r="O11" s="8" t="n">
         <v>0.9584727017005498</v>
       </c>
-      <c r="P11" s="7" t="n">
+      <c r="P11" s="8" t="n">
         <v>0.9568923411328473</v>
       </c>
-      <c r="Q11" s="7" t="n">
+      <c r="Q11" s="8" t="n">
         <v>0.9591708221455056</v>
       </c>
-      <c r="R11" s="9" t="inlineStr">
+      <c r="R11" s="10" t="inlineStr">
         <is>
           <t>Qwen 7B</t>
         </is>
       </c>
-      <c r="S11" s="7" t="n">
+      <c r="S11" s="8" t="n">
         <v>0.9109090909090912</v>
       </c>
-      <c r="T11" s="7" t="n">
+      <c r="T11" s="8" t="n">
         <v>0.9054545454545457</v>
       </c>
-      <c r="U11" s="7" t="n">
+      <c r="U11" s="8" t="n">
         <v>0.9109090909090911</v>
       </c>
-      <c r="V11" s="10" t="inlineStr">
+      <c r="V11" s="11" t="inlineStr">
         <is>
           <t>tie</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="7">
+  <mergeCells count="10">
+    <mergeCell ref="A3:A5"/>
+    <mergeCell ref="A9:A11"/>
     <mergeCell ref="C1:F1"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="G1:J1"/>
     <mergeCell ref="S1:V1"/>
     <mergeCell ref="K1:N1"/>
+    <mergeCell ref="A6:A8"/>
     <mergeCell ref="O1:R1"/>
     <mergeCell ref="A1:A2"/>
   </mergeCells>
